--- a/StudyLogs/template/【資格学習記録】_名前.xlsx
+++ b/StudyLogs/template/【資格学習記録】_名前.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Project\StudyLogs\StudyLogs\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{993B9EA1-C778-4F36-A1F6-E1FDF12A6FAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DCE4BD2-145E-442D-A378-BCE13AB37AA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4080" yWindow="3675" windowWidth="28170" windowHeight="14655" xr2:uid="{1418F11E-6B35-4EF0-B5B4-2114BFC5FADF}"/>
+    <workbookView xWindow="4290" yWindow="4290" windowWidth="28170" windowHeight="14655" xr2:uid="{1418F11E-6B35-4EF0-B5B4-2114BFC5FADF}"/>
   </bookViews>
   <sheets>
     <sheet name="tmp" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
+    <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
   </numFmts>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
@@ -498,10 +498,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="56" fontId="0" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -531,7 +531,7 @@
     <xf numFmtId="56" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1">
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -540,9 +540,32 @@
   </cellStyles>
   <dxfs count="8">
     <dxf>
-      <numFmt numFmtId="177" formatCode="yyyy/m/d;@"/>
+      <numFmt numFmtId="176" formatCode="yyyy/m/d;@"/>
       <border diagonalUp="0" diagonalDown="0">
         <left/>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+        <vertical style="thin">
+          <color indexed="64"/>
+        </vertical>
+        <horizontal style="thin">
+          <color indexed="64"/>
+        </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="14" formatCode="0.00%"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
@@ -566,28 +589,6 @@
           <color indexed="64"/>
         </left>
         <right/>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-        <vertical style="thin">
-          <color indexed="64"/>
-        </vertical>
-        <horizontal style="thin">
-          <color indexed="64"/>
-        </horizontal>
-      </border>
-    </dxf>
-    <dxf>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
         <top style="thin">
           <color indexed="64"/>
         </top>
@@ -712,8 +713,8 @@
     <tableColumn id="1" xr3:uid="{DA93D1E5-F426-4D73-ADC0-912D94F85398}" name="日付" dataDxfId="0"/>
     <tableColumn id="2" xr3:uid="{C9302303-6026-4235-B6FD-3B7D5A33BEFD}" name="学習時間(分)" dataDxfId="4"/>
     <tableColumn id="3" xr3:uid="{192E4D27-401F-4EEE-916F-93FF195AFDF6}" name="内容" dataDxfId="3"/>
-    <tableColumn id="4" xr3:uid="{F4224F36-FFCB-412E-91D7-757C82CD1580}" name="進捗率" dataDxfId="2"/>
-    <tableColumn id="5" xr3:uid="{1AA2D08A-115C-4DEE-8A9C-D6B117AF62FD}" name="備考" dataDxfId="1"/>
+    <tableColumn id="4" xr3:uid="{F4224F36-FFCB-412E-91D7-757C82CD1580}" name="進捗率" dataDxfId="1"/>
+    <tableColumn id="5" xr3:uid="{1AA2D08A-115C-4DEE-8A9C-D6B117AF62FD}" name="備考" dataDxfId="2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1116,11 +1117,11 @@
       </c>
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.4">
-      <c r="B10" s="22"/>
+      <c r="B10" s="12"/>
       <c r="C10" s="9"/>
       <c r="D10" s="10"/>
-      <c r="E10" s="11"/>
-      <c r="F10" s="12"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="11"/>
     </row>
   </sheetData>
   <mergeCells count="6">
